--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486911_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486911_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1557</v>
+        <v>2.2175</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7394</v>
+        <v>5.1274</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5838</v>
+        <v>-2.9098</v>
       </c>
       <c r="G2" t="n">
         <v>0.8534</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5179</v>
+        <v>1.5798</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7432</v>
+        <v>1.1311</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7748</v>
+        <v>0.4487</v>
       </c>
       <c r="V2" t="n">
         <v>1.8378</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6393</v>
+        <v>0.9952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7648</v>
+        <v>0.269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.444</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5362</v>
+        <v>0.8921</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.5036</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5367</v>
+        <v>0.3885</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1088</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4791</v>
+        <v>0.0408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.827</v>
+        <v>0.1219</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3479</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0989</v>
@@ -766,13 +766,13 @@
         <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2432</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3675</v>
+        <v>0.6624</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1243</v>
+        <v>0.1425</v>
       </c>
       <c r="V4" t="n">
         <v>1.1561</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1445</v>
+        <v>-0.9213</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0081</v>
+        <v>-0.9035</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1364</v>
+        <v>-0.0178</v>
       </c>
       <c r="G5" t="n">
         <v>0.8222</v>
@@ -844,13 +844,13 @@
         <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1186</v>
+        <v>0.1046</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U5" t="n">
-        <v>0.079</v>
+        <v>0.1976</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>J. SÁNCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.614</v>
+        <v>-1.3338</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3141</v>
+        <v>-2.1477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.8139</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8674</v>
+        <v>-2.2171</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6069</v>
+        <v>-1.8749</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2606</v>
+        <v>-0.3422</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9999</v>
+        <v>-1.1442</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4477</v>
+        <v>-1.6833</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4476</v>
+        <v>0.5391</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8676</v>
+        <v>-1.0729</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0546</v>
+        <v>-0.1917</v>
       </c>
       <c r="O6" t="n">
-        <v>0.187</v>
+        <v>-0.8813</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5676</v>
+        <v>0.1153</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1704</v>
+        <v>0.0232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3973</v>
+        <v>0.0921</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1088</v>
+        <v>0.768</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4579</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3491</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>D. JACKSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8683</v>
+        <v>-1.3875</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6896</v>
+        <v>-0.132</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1786</v>
+        <v>-1.2555</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7365</v>
+        <v>-1.2679</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0867</v>
+        <v>2.4078</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6498</v>
+        <v>-3.6757</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6974</v>
+        <v>2.5302</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6974</v>
+        <v>3.7934</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.2633</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0392</v>
+        <v>-3.7981</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3893</v>
+        <v>-1.3857</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6498</v>
+        <v>-2.4124</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1317</v>
+        <v>0.7285</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0077</v>
+        <v>0.5268</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1395</v>
+        <v>0.2017</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1787</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.2875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2166</v>
+        <v>-1.6591</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7637</v>
+        <v>-0.4804</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5471</v>
+        <v>-1.1786</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2171</v>
+        <v>-1.7365</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8749</v>
+        <v>-1.0867</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3422</v>
+        <v>-0.6498</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1442</v>
+        <v>-0.6974</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6833</v>
+        <v>-0.6974</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5391</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0729</v>
+        <v>-1.0392</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1917</v>
+        <v>-0.3893</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8813</v>
+        <v>-0.6498</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7675</v>
+        <v>0.0775</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5928</v>
+        <v>0.2169</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1747</v>
+        <v>-0.1395</v>
       </c>
       <c r="V8" t="n">
-        <v>0.768</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. JACKSON</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.394</v>
+        <v>-1.6963</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3757</v>
+        <v>-2.2482</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0184</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2679</v>
+        <v>-1.8674</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4078</v>
+        <v>-0.6069</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6757</v>
+        <v>-1.2606</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5302</v>
+        <v>-0.9999</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7934</v>
+        <v>0.4477</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2633</v>
+        <v>-1.4476</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.7981</v>
+        <v>-0.8676</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3857</v>
+        <v>-1.0546</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4124</v>
+        <v>0.187</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-3.0801</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.278</v>
+        <v>0.4853</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7169</v>
+        <v>0.2362</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4388</v>
+        <v>0.249</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1787</v>
+        <v>-0.1088</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1088</v>
+        <v>-0.4579</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2875</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2946</v>
+        <v>-2.9135</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6662</v>
+        <v>-0.1346</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6284</v>
+        <v>-2.779</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2021</v>
+        <v>-4.8556</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6415</v>
+        <v>-0.8535</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4395</v>
+        <v>-4.0021</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1575</v>
+        <v>-1.8438</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6974</v>
+        <v>0.1168</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8549</v>
+        <v>-1.9606</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3596</v>
+        <v>-3.0118</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9442</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4154</v>
+        <v>-2.0415</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.6962</v>
+        <v>1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.1068</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>0.425</v>
+        <v>0.6402</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1045</v>
+        <v>0.5306</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3205</v>
+        <v>0.1096</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1786</v>
+        <v>0.0698</v>
       </c>
       <c r="W10" t="n">
         <v>1.1786</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8029</v>
+        <v>-3.461</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8165</v>
+        <v>-1.7436</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9865</v>
+        <v>-1.7174</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8556</v>
+        <v>-1.2021</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8535</v>
+        <v>-1.6415</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.0021</v>
+        <v>0.4395</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8438</v>
+        <v>1.1575</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1168</v>
+        <v>-0.6974</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9606</v>
+        <v>1.8549</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0118</v>
+        <v>-2.3596</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.9442</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0415</v>
+        <v>-1.4154</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2321</v>
+        <v>-3.6962</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.1068</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2492</v>
+        <v>0.2586</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1513</v>
+        <v>0.027</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0979</v>
+        <v>0.2316</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0698</v>
+        <v>1.1786</v>
       </c>
       <c r="W11" t="n">
         <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.774</v>
+        <v>-6.0691</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8094</v>
+        <v>-2.1934</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9646</v>
+        <v>-3.8757</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7257</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2701</v>
+        <v>0.4349</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2171</v>
+        <v>0.3989</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0529</v>
+        <v>0.036</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1088</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.8348</v>
+        <v>-16.1881</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1121</v>
+        <v>-4.465100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.7229</v>
+        <v>-11.7228</v>
       </c>
       <c r="G13" t="n">
         <v>-13.8516</v>
@@ -1468,10 +1468,10 @@
         <v>11.2939</v>
       </c>
       <c r="S13" t="n">
-        <v>4.474799999999999</v>
+        <v>6.121700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.517100000000001</v>
+        <v>4.1637</v>
       </c>
       <c r="U13" t="n">
         <v>1.9578</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.418</v>
+        <v>7.4676</v>
       </c>
       <c r="E14" t="n">
-        <v>3.514</v>
+        <v>4.2462</v>
       </c>
       <c r="F14" t="n">
-        <v>2.904</v>
+        <v>3.2213</v>
       </c>
       <c r="G14" t="n">
         <v>4.8613</v>
@@ -1546,13 +1546,13 @@
         <v>3.2855</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4002</v>
+        <v>-0.3506</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7827</v>
+        <v>-0.0505</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.3001</v>
       </c>
       <c r="V14" t="n">
         <v>0.6982</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8151</v>
+        <v>6.9832</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3028</v>
+        <v>5.035</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5122</v>
+        <v>1.9481</v>
       </c>
       <c r="G15" t="n">
         <v>5.2076</v>
@@ -1624,13 +1624,13 @@
         <v>4.5175</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1852</v>
+        <v>-1.0171</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4415</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7437</v>
+        <v>-0.3078</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6982</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2836</v>
+        <v>3.9017</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8112</v>
+        <v>1.4974</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4724</v>
+        <v>2.4043</v>
       </c>
       <c r="G16" t="n">
         <v>3.2293</v>
@@ -1702,13 +1702,13 @@
         <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5204</v>
+        <v>0.1386</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3757</v>
+        <v>0.0619</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1447</v>
+        <v>0.0766</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6982</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1881</v>
+        <v>2.7863</v>
       </c>
       <c r="E17" t="n">
-        <v>4.5978</v>
+        <v>3.5518</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4097</v>
+        <v>-0.7654</v>
       </c>
       <c r="G17" t="n">
         <v>3.7665</v>
@@ -1780,13 +1780,13 @@
         <v>2.6694</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6187</v>
+        <v>0.2169</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1776</v>
+        <v>0.1315</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4411</v>
+        <v>0.0854</v>
       </c>
       <c r="V17" t="n">
         <v>0.2402</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8239</v>
+        <v>2.3382</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5446</v>
+        <v>-0.0216</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3685</v>
+        <v>2.3598</v>
       </c>
       <c r="G18" t="n">
         <v>1.2283</v>
@@ -1858,13 +1858,13 @@
         <v>2.6694</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9588</v>
+        <v>-0.4445</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7905</v>
+        <v>-0.2674</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1683</v>
+        <v>-0.1771</v>
       </c>
       <c r="V18" t="n">
         <v>0.9384</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3448</v>
+        <v>0.2454</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5381</v>
+        <v>-0.7473</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8829</v>
+        <v>0.9928</v>
       </c>
       <c r="G19" t="n">
         <v>1.4355</v>
@@ -1936,13 +1936,13 @@
         <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4459</v>
+        <v>-0.5453</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0386</v>
+        <v>-0.1706</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4845</v>
+        <v>-0.3747</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8768</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3776</v>
+        <v>0.1437</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0247</v>
+        <v>-0.7109</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6471</v>
+        <v>0.8546</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2869</v>
@@ -2014,13 +2014,13 @@
         <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9388</v>
+        <v>-0.4175</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.651</v>
+        <v>-0.3372</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2878</v>
+        <v>-0.0803</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-1.6151</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9378</v>
+        <v>-1.4669</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.652</v>
+        <v>-0.1482</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2809</v>
+        <v>-1.6151</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2073</v>
+        <v>-0.8047</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0736</v>
+        <v>-0.8104</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2917</v>
+        <v>0.1023</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0419</v>
+        <v>0.1947</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7502</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5726</v>
+        <v>-1.7174</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2492</v>
+        <v>-0.9994</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3234</v>
+        <v>-0.7181</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7392</v>
+        <v>-0.5812</v>
       </c>
       <c r="T21" t="n">
-        <v>1.104</v>
+        <v>-0.5425</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3648</v>
+        <v>-0.0386</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2259</v>
+        <v>-0.2402</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4579</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7679</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8992</v>
+        <v>-1.8195</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4474</v>
+        <v>-0.1083</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3466</v>
+        <v>-1.7113</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6938</v>
+        <v>-1.2809</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3861</v>
+        <v>-0.2073</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3077</v>
+        <v>-1.0736</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5995</v>
+        <v>0.2917</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0584</v>
+        <v>1.0419</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6579</v>
+        <v>-0.7502</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0943</v>
+        <v>-1.5726</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4445</v>
+        <v>-1.2492</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6498</v>
+        <v>-0.3234</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4107</v>
+        <v>-0.3662</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1317</v>
+        <v>0.0579</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2789</v>
+        <v>-0.4241</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.2259</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>-0.4579</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0475</v>
+        <v>-1.8992</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7807</v>
+        <v>0.4474</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2668</v>
+        <v>-2.3466</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6151</v>
+        <v>-1.6938</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8047</v>
+        <v>-0.3861</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8104</v>
+        <v>-1.3077</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1023</v>
+        <v>-0.5995</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1947</v>
+        <v>0.0584</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.6579</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7174</v>
+        <v>-1.0943</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9994</v>
+        <v>-0.4445</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7181</v>
+        <v>-0.6498</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0135</v>
+        <v>-0.4107</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8563</v>
+        <v>-0.1317</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1572</v>
+        <v>-0.2789</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>17.835</v>
+        <v>18.5323</v>
       </c>
       <c r="E24" t="n">
-        <v>11.7229</v>
+        <v>11.7228</v>
       </c>
       <c r="F24" t="n">
-        <v>6.112</v>
+        <v>6.8094</v>
       </c>
       <c r="G24" t="n">
         <v>13.8518</v>
@@ -2296,7 +2296,7 @@
         <v>6.537000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>7.314500000000001</v>
+        <v>7.314499999999999</v>
       </c>
       <c r="J24" t="n">
         <v>23.6193</v>
@@ -2314,7 +2314,7 @@
         <v>-3.863</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.904599999999999</v>
+        <v>-5.9046</v>
       </c>
       <c r="P24" t="n">
         <v>12.3206</v>
@@ -2326,22 +2326,22 @@
         <v>23.6143</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.4748</v>
+        <v>-3.7776</v>
       </c>
       <c r="T24" t="n">
         <v>-1.9578</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5168</v>
+        <v>-1.8196</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.862500000000001</v>
+        <v>-3.8625</v>
       </c>
       <c r="W24" t="n">
         <v>1.355</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.2172</v>
+        <v>-5.217200000000001</v>
       </c>
     </row>
   </sheetData>
